--- a/report5.xlsx
+++ b/report5.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708"/>
+    <workbookView windowWidth="23040" windowHeight="9708" tabRatio="162"/>
   </bookViews>
   <sheets>
     <sheet name="report4" sheetId="1" r:id="rId1"/>
@@ -27,17 +27,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="157">
+  <si>
+    <t>user_input</t>
+  </si>
+  <si>
+    <t>response</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
   <si>
     <t>retrieved_contexts</t>
   </si>
   <si>
-    <t>response</t>
-  </si>
-  <si>
-    <t>reference</t>
-  </si>
-  <si>
     <t>llm_context_precision_with_reference</t>
   </si>
   <si>
@@ -50,43 +53,52 @@
     <t>faithfulness</t>
   </si>
   <si>
-    <t>['Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Xếp hạng của trường Đại học Bách khoa Thành phố Hồ Chí Minh là bao nhiêu\nA: Trường đạt các vị trí trong bảng xếp hạng Round University Ranking (RUR) năm 2024 như sau: 866 trong bảng xếp hạng “World University Rankings”, 432 trong bảng xếp hạng “RUR Reputation Rankings”, 776 trong bảng xếp hạng “RUR Academic Rankings”', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.']</t>
-  </si>
-  <si>
-    <t>Trường chúng tôi được thành lập từ năm 1957 và tên viết tắt là HCMUT.</t>
+    <t>Trường Đại học Bách khoa TP.HCM được thành lập năm nào và tên viết tắt là gì?</t>
+  </si>
+  <si>
+    <t>Trường chúng tôi được thành lập từ năm 1957 và có tên viết tắt là HCMUT.</t>
   </si>
   <si>
     <t>Trường Đại học Bách khoa TP.HCM được thành lập năm 1957 và có tên viết tắt là HCMUT.</t>
   </si>
   <si>
+    <t>['Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.']</t>
+  </si>
+  <si>
     <t>0.7555880813150386</t>
   </si>
   <si>
-    <t>['Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Địa chỉ email của trường là gì?\nA: Địa chỉ email của Trường Đại học Bách khoa - ĐHQG-HCM là info@hcmut.edu.vn.', 'Q: Trường có ký túc xá cho sinh viên không ạ\nA: Trường chúng tôi có kí túc xá giành riêng cho sinh viên bách khoa ở số 497 Hòa Hảo, Phường 7, Quận 10, Tp. Hồ Chí Minh. Còn nếu bạn học ở cơ sở 2 thì hoàn toàn có thể ở kí túc xá đại học quốc gia.']</t>
-  </si>
-  <si>
-    <t>Địa chỉ cơ sở 1 của trường là 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.</t>
+    <t>Địa chỉ cơ sở 1 của trường Bách khoa TP.HCM ở đâu vậy ạ?</t>
+  </si>
+  <si>
+    <t>Địa chỉ cơ sở 1 của Trường Đại học Bách khoa TP.HCM là 268 Lý Thường Kiệt, Phường 14, Quận 10, Thành Phố Hồ Chí Minh.</t>
   </si>
   <si>
     <t>Cơ sở 1 của trường nằm tại 268 Lý Thường Kiệt, Phường 14, Quận 10, Thành phố Hồ Chí Minh.</t>
   </si>
   <si>
+    <t>['Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Địa chỉ cụ thể của trường ở đâu\nA: Trường chúng tôi có hai cơ cở, địa chỉ cơ sở một là ở 268 Lý Thường Kiệt, Phường 14, Quận 10, Thành Phố Hồ Chí Minh, địa chỉ cơ sở hai là Khu phố Tân Lập, Phường Đông Hòa, TP. Dĩ An, Tỉnh Bình Dương', 'Q: Địa chỉ email của trường là gì?\nA: Địa chỉ email của Trường Đại học Bách khoa - ĐHQG-HCM là info@hcmut.edu.vn.', 'Q: Trường mình có mấy chi nhánh ?\nA: Trường mình có 2 chi nhánh: cơ sở 1 ở Lý Thường Kiệt quận 10 thành phố Hồ Chí Minh, còn cơ sở 2 ở Dĩ An']</t>
+  </si>
+  <si>
     <t>0.7932350259623007</t>
   </si>
   <si>
-    <t>['Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Trường có ký túc xá cho sinh viên không ạ\nA: Trường chúng tôi có kí túc xá giành riêng cho sinh viên bách khoa ở số 497 Hòa Hảo, Phường 7, Quận 10, Tp. Hồ Chí Minh. Còn nếu bạn học ở cơ sở 2 thì hoàn toàn có thể ở kí túc xá đại học quốc gia.', 'Q: Em có thể liên hệ số điện thoại nào để được tư vấn chung\nA: Để được tư vấn bạn có thể liên hệ số điện thoại: 02838647256', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.']</t>
-  </si>
-  <si>
-    <t>Để được tư vấn bạn có thể liên hệ số điện thoại: 02838647256</t>
+    <t>Nếu em muốn gọi điện hỏi thông tin tuyển sinh thì gọi số nào ạ?</t>
+  </si>
+  <si>
+    <t>Để được tư vấn bạn có thể liên hệ số điện thoại: 02838647256.</t>
   </si>
   <si>
     <t>Bạn có thể gọi đến số điện thoại 02838647256 để được tư vấn.</t>
   </si>
   <si>
+    <t>['Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Địa chỉ email của trường là gì?\nA: Địa chỉ email của Trường Đại học Bách khoa - ĐHQG-HCM là info@hcmut.edu.vn.', 'Q: Em có thể tìm kiếm thông tin hướng dẫn nhập học ở đâu?\nA: Bạn có thể xem hướng dẫn nhập học ở đây: https://hcmut.edu.vn/tuyen-sinh/dai-hoc-chinh-quy/thong-tin-nhap-hoc', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Em có thể liên hệ số điện thoại nào để được tư vấn chung\nA: Để được tư vấn bạn có thể liên hệ số điện thoại: 02838647256']</t>
+  </si>
+  <si>
     <t>0.6909104384661877</t>
   </si>
   <si>
-    <t>['Q: Trường có những phương thức xét tuyển nào cho năm học 2025-2026\nA: Trường chúng tôi năm học 2025-2026 có 2 phương thức tuyển sinh: Phương thức 1 là xét tuyển thẳng theo quy chế tuyển sinh của Bộ giáo dục và đào tạo từ 1-5% tổng chỉ tiêu, Phương thức 2 là xét tuyển tổng hợp, từ 95 - 99% tổng chỉ tiêu. ', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu', 'Q: Phương thức xét tuyển tổng hợp tính điểm như thế nào?\nA: Phương thức xét tuyển tổng hợp của Trường Đại học Bách khoa - ĐHQG-HCM tính điểm dựa trên công thức sau:[Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100)Trong đó:[Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100)Tùy thuộc vào đối tượng xét tuyển, các thành phần điểm sẽ được tính khác nhau. Ví dụ, đối với thí sinh có kết quả thi Đánh giá Năng lực ĐHQG-HCM, điểm năng lực được tính dựa trên điểm thi này.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là bao nhiêu?\nA: Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là 84,16']</t>
+    <t>Năm 2025-2026 trường có mấy phương thức xét tuyển và tỉ lệ chỉ tiêu mỗi phương thức là bao nhiêu?</t>
   </si>
   <si>
     <t>Trường chúng tôi năm học 2025-2026 có 2 phương thức tuyển sinh: Phương thức 1 là xét tuyển thẳng (1-5% tổng chỉ tiêu), Phương thức 2 là xét tuyển tổng hợp (95-99% tổng chỉ tiêu).</t>
@@ -95,10 +107,13 @@
     <t>Trường có 2 phương thức tuyển sinh: Phương thức 1 là xét tuyển thẳng theo quy chế của Bộ GD&amp;ĐT, chiếm 1–5% tổng chỉ tiêu; Phương thức 2 là xét tuyển tổng hợp, chiếm 95–99% tổng chỉ tiêu.</t>
   </si>
   <si>
+    <t>['Q: Trường có những phương thức xét tuyển nào cho năm học 2025-2026\nA: Trường chúng tôi năm học 2025-2026 có 2 phương thức tuyển sinh: Phương thức 1 là xét tuyển thẳng theo quy chế tuyển sinh của Bộ giáo dục và đào tạo từ 1-5% tổng chỉ tiêu, Phương thức 2 là xét tuyển tổng hợp, từ 95 - 99% tổng chỉ tiêu. ', 'Q: Phương thức xét tuyển tổng hợp tính điểm như thế nào?\nA: Phương thức xét tuyển tổng hợp của Trường Đại học Bách khoa - ĐHQG-HCM tính điểm dựa trên công thức sau:[Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100)Trong đó:[Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100)Tùy thuộc vào đối tượng xét tuyển, các thành phần điểm sẽ được tính khác nhau. Ví dụ, đối với thí sinh có kết quả thi Đánh giá Năng lực ĐHQG-HCM, điểm năng lực được tính dựa trên điểm thi này.', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.']</t>
+  </si>
+  <si>
     <t>0.858270973090184</t>
   </si>
   <si>
-    <t>['Q: Mã trường khi đăng ký tuyển sinh là gì\nA: Mã trường chúng tôi là QSB', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ']</t>
+    <t>Mã trường khi em đăng ký xét tuyển vào Bách khoa là gì?</t>
   </si>
   <si>
     <t>Mã trường chúng tôi là QSB.</t>
@@ -107,10 +122,13 @@
     <t>Mã trường của Trường Đại học Bách khoa - ĐHQG-HCM là QSB.</t>
   </si>
   <si>
+    <t>['Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Mã trường khi đăng ký tuyển sinh là gì\nA: Mã trường chúng tôi là QSB', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Trường có những phương thức xét tuyển nào cho năm học 2025-2026\nA: Trường chúng tôi năm học 2025-2026 có 2 phương thức tuyển sinh: Phương thức 1 là xét tuyển thẳng theo quy chế tuyển sinh của Bộ giáo dục và đào tạo từ 1-5% tổng chỉ tiêu, Phương thức 2 là xét tuyển tổng hợp, từ 95 - 99% tổng chỉ tiêu. ']</t>
+  </si>
+  <si>
     <t>0.7997399176312205</t>
   </si>
   <si>
-    <t>['Q: Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là bao nhiêu?\nA: Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là 84,16', 'Q: Phương thức xét tuyển tổng hợp tính điểm như thế nào?\nA: Phương thức xét tuyển tổng hợp của Trường Đại học Bách khoa - ĐHQG-HCM tính điểm dựa trên công thức sau:[Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100)Trong đó:[Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100)Tùy thuộc vào đối tượng xét tuyển, các thành phần điểm sẽ được tính khác nhau. Ví dụ, đối với thí sinh có kết quả thi Đánh giá Năng lực ĐHQG-HCM, điểm năng lực được tính dựa trên điểm thi này.', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu', 'Q: Điểm chuẩn ngành Khoa học Máy tính các năm gần đây như thế nào?\nA: Điểm chuẩn ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM trong các năm gần đây có sự biến động. Cụ thể, điểm chuẩn của ngành này trong năm 2025 là 85.41 cho chương trình chính quy và 72.90 cho chương trình liên kết quốc tế với Úc, New Zealand, Mỹ.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957']</t>
+    <t>Điểm chuẩn ngành Khoa học Máy tính theo phương thức xét tuyển tổng hợp năm 2024 là bao nhiêu?</t>
   </si>
   <si>
     <t>Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là 84,16.</t>
@@ -119,22 +137,29 @@
     <t>Điểm chuẩn ngành Khoa học Máy tính theo phương thức xét tuyển tổng hợp năm 2024 là 84,16 điểm (thang 100).</t>
   </si>
   <si>
+    <t>['Q: Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là bao nhiêu?\nA: Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là 84,16', 'Q: Điểm chuẩn ngành Khoa học Máy tính các năm gần đây như thế nào?\nA: Điểm chuẩn ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM trong các năm gần đây có sự biến động. Cụ thể, điểm chuẩn của ngành này trong năm 2025 là 85.41 cho chương trình chính quy và 72.90 cho chương trình liên kết quốc tế với Úc, New Zealand, Mỹ.', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu', 'Q: Phương thức xét tuyển tổng hợp tính điểm như thế nào?\nA: Phương thức xét tuyển tổng hợp của Trường Đại học Bách khoa - ĐHQG-HCM tính điểm dựa trên công thức sau:[Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100)Trong đó:[Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100)Tùy thuộc vào đối tượng xét tuyển, các thành phần điểm sẽ được tính khác nhau. Ví dụ, đối với thí sinh có kết quả thi Đánh giá Năng lực ĐHQG-HCM, điểm năng lực được tính dựa trên điểm thi này.', 'Q: Chương trình tiên tiến Khóa học Máy tính khác gì so với chương trình thường?\nA: Chương trình Tiên tiến ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM được đào tạo hoàn toàn bằng tiếng Anh. Giáo trình được chuyển giao từ Đại học Illinois Urbana Champaign (Mỹ) và cải tiến. Học phí khoảng 40 triệu đồng/học kỳ. Chương trình này có chuẩn tiếng Anh đầu vào là IELTS (Academic) ≥ 6.0 / TOEFL iBT ≥ 79/ TOEIC Nghe - Đọc ≥ 730 &amp; Nói - Viết ≥ 280.']</t>
+  </si>
+  <si>
     <t>0.8720313401772823</t>
   </si>
   <si>
-    <t>['Q: Phương thức xét tuyển tổng hợp tính điểm như thế nào?\nA: Phương thức xét tuyển tổng hợp của Trường Đại học Bách khoa - ĐHQG-HCM tính điểm dựa trên công thức sau:[Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100)Trong đó:[Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100)Tùy thuộc vào đối tượng xét tuyển, các thành phần điểm sẽ được tính khác nhau. Ví dụ, đối với thí sinh có kết quả thi Đánh giá Năng lực ĐHQG-HCM, điểm năng lực được tính dựa trên điểm thi này.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Điểm thi Đánh giá Năng lực của ĐHQG-HCM có trọng số bao nhiêu?\nA: Điểm thi Đánh giá Năng lực của ĐHQG-HCM chiếm trọng số 70% trong công thức tính điểm xét tuyển tổng hợp cho đối tượng có kết quả thi này. Cụ thể, điểm năng lực được tính bằng [Điểm ĐGNL có hệ số Toán × 2] / 15.', 'Q: Trường có những phương thức xét tuyển nào cho năm học 2025-2026\nA: Trường chúng tôi năm học 2025-2026 có 2 phương thức tuyển sinh: Phương thức 1 là xét tuyển thẳng theo quy chế tuyển sinh của Bộ giáo dục và đào tạo từ 1-5% tổng chỉ tiêu, Phương thức 2 là xét tuyển tổng hợp, từ 95 - 99% tổng chỉ tiêu. ', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh']</t>
-  </si>
-  <si>
-    <t>Công thức tính điểm xét tuyển tổng hợp của Trường Đại học Bách khoa TP.HCM gồm: [Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100). Trong đó: [Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100).</t>
+    <t>Công thức tính điểm xét tuyển tổng hợp của trường Bách khoa gồm những thành phần nào?</t>
+  </si>
+  <si>
+    <t>Công thức tính điểm xét tuyển tổng hợp của Trường Đại học Bách khoa TP.HCM là: [Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100).
+Trong đó: [Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPT quy đổi] × 20% + [Điểm học THPT quy đổi] × 10% (Thang điểm 100).</t>
   </si>
   <si>
     <t>Điểm xét tuyển = Điểm học lực + Điểm ưu tiên (thang 100). Trong đó Điểm học lực = Điểm năng lực × 70% + Điểm THPT quốc gia quy đổi × 20% + Điểm học THPT quy đổi × 10%. Điểm thi Đánh giá Năng lực ĐHQG-HCM chiếm trọng số 70% trong thành phần điểm năng lực.</t>
   </si>
   <si>
+    <t>['Q: Phương thức xét tuyển tổng hợp tính điểm như thế nào?\nA: Phương thức xét tuyển tổng hợp của Trường Đại học Bách khoa - ĐHQG-HCM tính điểm dựa trên công thức sau:[Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100)Trong đó:[Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100)Tùy thuộc vào đối tượng xét tuyển, các thành phần điểm sẽ được tính khác nhau. Ví dụ, đối với thí sinh có kết quả thi Đánh giá Năng lực ĐHQG-HCM, điểm năng lực được tính dựa trên điểm thi này.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Điểm thi Đánh giá Năng lực của ĐHQG-HCM có trọng số bao nhiêu?\nA: Điểm thi Đánh giá Năng lực của ĐHQG-HCM chiếm trọng số 70% trong công thức tính điểm xét tuyển tổng hợp cho đối tượng có kết quả thi này. Cụ thể, điểm năng lực được tính bằng [Điểm ĐGNL có hệ số Toán × 2] / 15.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.']</t>
+  </si>
+  <si>
     <t>0.8444692484863179</t>
   </si>
   <si>
-    <t>['Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu', 'Q: Điểm chuẩn ngành Khoa học Máy tính các năm gần đây như thế nào?\nA: Điểm chuẩn ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM trong các năm gần đây có sự biến động. Cụ thể, điểm chuẩn của ngành này trong năm 2025 là 85.41 cho chương trình chính quy và 72.90 cho chương trình liên kết quốc tế với Úc, New Zealand, Mỹ.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Câu lạc bộ lập trình hoặc AI của khoa CSE tên là gì?\nA: Sinh viên ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM có cơ hội tham gia các hoạt động nghiên cứu khoa học và các câu lạc bộ chuyên môn. Tuy nhiên, tôi không có thông tin cụ thể về tên của câu lạc bộ lập trình hoặc AI của khoa CSE.', 'Q: Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là bao nhiêu?\nA: Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là 84,16']</t>
+    <t>Em đang học lớp 12 và muốn biết ngành Khoa học Máy tính năm 2025 lấy bao nhiêu chỉ tiêu?</t>
   </si>
   <si>
     <t>Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu.</t>
@@ -143,10 +168,13 @@
     <t>Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - ĐHQG-HCM là 150 chỉ tiêu.</t>
   </si>
   <si>
+    <t>['Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu', 'Q: Điểm chuẩn ngành Khoa học Máy tính các năm gần đây như thế nào?\nA: Điểm chuẩn ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM trong các năm gần đây có sự biến động. Cụ thể, điểm chuẩn của ngành này trong năm 2025 là 85.41 cho chương trình chính quy và 72.90 cho chương trình liên kết quốc tế với Úc, New Zealand, Mỹ.', 'Q: Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là bao nhiêu?\nA: Điểm chuẩn theo phương thức xét tuyển tổng hợp năm 2024 của ngành Khoa học máy tính là 84,16', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ']</t>
+  </si>
+  <si>
     <t>0.8274739329647979</t>
   </si>
   <si>
-    <t>['Q: Thời gian nộp hồ sơ xét tuyển bằng điểm thi THPT năm 2025 là khi nào\nA: Thời gian xét tuyển bằng điểm thi THPT là từ ngày 21/4/2025 đến 17 giờ ngày 28/4/2025', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu', 'Q: Điểm chuẩn ngành Khoa học Máy tính các năm gần đây như thế nào?\nA: Điểm chuẩn ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM trong các năm gần đây có sự biến động. Cụ thể, điểm chuẩn của ngành này trong năm 2025 là 85.41 cho chương trình chính quy và 72.90 cho chương trình liên kết quốc tế với Úc, New Zealand, Mỹ.', 'Q: Phương thức xét tuyển tổng hợp tính điểm như thế nào?\nA: Phương thức xét tuyển tổng hợp của Trường Đại học Bách khoa - ĐHQG-HCM tính điểm dựa trên công thức sau:[Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100)Trong đó:[Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100)Tùy thuộc vào đối tượng xét tuyển, các thành phần điểm sẽ được tính khác nhau. Ví dụ, đối với thí sinh có kết quả thi Đánh giá Năng lực ĐHQG-HCM, điểm năng lực được tính dựa trên điểm thi này.', 'Q: Trường có những phương thức xét tuyển nào cho năm học 2025-2026\nA: Trường chúng tôi năm học 2025-2026 có 2 phương thức tuyển sinh: Phương thức 1 là xét tuyển thẳng theo quy chế tuyển sinh của Bộ giáo dục và đào tạo từ 1-5% tổng chỉ tiêu, Phương thức 2 là xét tuyển tổng hợp, từ 95 - 99% tổng chỉ tiêu. ']</t>
+    <t>Nộp hồ sơ xét tuyển bằng điểm thi THPT năm 2025 trong khoảng thời gian nào vậy ạ?</t>
   </si>
   <si>
     <t>Thời gian xét tuyển bằng điểm thi THPT là từ ngày 21/4/2025 đến 17 giờ ngày 28/4/2025.</t>
@@ -155,22 +183,25 @@
     <t>Thời gian nộp hồ sơ xét tuyển bằng điểm thi THPT năm 2025 là từ ngày 21/4/2025 đến 17 giờ ngày 28/4/2025.</t>
   </si>
   <si>
+    <t>['Q: Thời gian nộp hồ sơ xét tuyển bằng điểm thi THPT năm 2025 là khi nào\nA: Thời gian xét tuyển bằng điểm thi THPT là từ ngày 21/4/2025 đến 17 giờ ngày 28/4/2025', 'Q: Điều kiện để xét tuyển bằng học bạ THPT là gì\nA: Thí sinh cần có học bạ THPT với điểm trung bình các môn học đạt yêu cầu của trường, nộp đầy đủ hồ sơ theo quy định và đáp ứng các tiêu chí khác như độ tuổi và thời gian tốt nghiệp không quá 2 năm so với năm dự tuyển.', 'Q: Phương thức xét tuyển tổng hợp tính điểm như thế nào?\nA: Phương thức xét tuyển tổng hợp của Trường Đại học Bách khoa - ĐHQG-HCM tính điểm dựa trên công thức sau:[Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100)Trong đó:[Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100)Tùy thuộc vào đối tượng xét tuyển, các thành phần điểm sẽ được tính khác nhau. Ví dụ, đối với thí sinh có kết quả thi Đánh giá Năng lực ĐHQG-HCM, điểm năng lực được tính dựa trên điểm thi này.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Trường có những phương thức xét tuyển nào cho năm học 2025-2026\nA: Trường chúng tôi năm học 2025-2026 có 2 phương thức tuyển sinh: Phương thức 1 là xét tuyển thẳng theo quy chế tuyển sinh của Bộ giáo dục và đào tạo từ 1-5% tổng chỉ tiêu, Phương thức 2 là xét tuyển tổng hợp, từ 95 - 99% tổng chỉ tiêu. ']</t>
+  </si>
+  <si>
     <t>0.7792704789294737</t>
   </si>
   <si>
-    <t>['Q: Thời gian công bố kết quả trúng tuyển là khi nào?\nA: Kết quả tuyển sinh sẽ được công bố trên Cổng tuyển sinh Mybk tại địa chỉ https://mybk.hcmut.edu.vn/tuyensinh. Bạn có thể tra cứu kết quả tuyển sinh tại đây và sẽ thấy thông tin về việc bạn trúng tuyển hay không, mã ngành trúng tuyển, mã nhập học, mã nhóm nhập học, và mã nhóm kiểm tra Anh văn xếp lớp (nếu có).', 'Q: Em có thể tra cứu kết quả tuyển sinh ở đâu?\nA: Bạn có thể tra cứu kết quả tuyển sinh theo đường link này: https://mybk.hcmut.edu.vn/tuyensinh/search', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Phương thức xét tuyển tổng hợp tính điểm như thế nào?\nA: Phương thức xét tuyển tổng hợp của Trường Đại học Bách khoa - ĐHQG-HCM tính điểm dựa trên công thức sau:[Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100)Trong đó:[Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100)Tùy thuộc vào đối tượng xét tuyển, các thành phần điểm sẽ được tính khác nhau. Ví dụ, đối với thí sinh có kết quả thi Đánh giá Năng lực ĐHQG-HCM, điểm năng lực được tính dựa trên điểm thi này.']</t>
-  </si>
-  <si>
-    <t>Bạn có thể tra cứu kết quả tuyển sinh tại https://mybk.hcmut.edu.vn/tuyensinh.</t>
+    <t>Để tra cứu kết quả trúng tuyển vào Bách khoa em vào trang web nào ạ?</t>
   </si>
   <si>
     <t>Bạn có thể tra cứu kết quả tuyển sinh tại: https://mybk.hcmut.edu.vn/tuyensinh/search</t>
   </si>
   <si>
+    <t>['Q: Em có thể tra cứu kết quả tuyển sinh ở đâu?\nA: Bạn có thể tra cứu kết quả tuyển sinh theo đường link này: https://mybk.hcmut.edu.vn/tuyensinh/search', 'Q: Thời gian công bố kết quả trúng tuyển là khi nào?\nA: Kết quả tuyển sinh sẽ được công bố trên Cổng tuyển sinh Mybk tại địa chỉ https://mybk.hcmut.edu.vn/tuyensinh. Bạn có thể tra cứu kết quả tuyển sinh tại đây và sẽ thấy thông tin về việc bạn trúng tuyển hay không, mã ngành trúng tuyển, mã nhập học, mã nhóm nhập học, và mã nhóm kiểm tra Anh văn xếp lớp (nếu có).', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Em có thể tìm kiếm thông tin hướng dẫn nhập học ở đâu?\nA: Bạn có thể xem hướng dẫn nhập học ở đây: https://hcmut.edu.vn/tuyen-sinh/dai-hoc-chinh-quy/thong-tin-nhap-hoc', 'Q: Địa chỉ email của trường là gì?\nA: Địa chỉ email của Trường Đại học Bách khoa - ĐHQG-HCM là info@hcmut.edu.vn.']</t>
+  </si>
+  <si>
     <t>0.7790604872381846</t>
   </si>
   <si>
-    <t>['Q: Hồ sơ cần chuẩn bị những giấy tờ gì để nhập học\nA: Hồ sơ nhập học bao gồm Phiếu đăng ký xét tuyển và tờ lý lịch, Giấy khai sinh (bản sao) hoặc công chứng, 2 ảnh 3x4, \t\nBằng tốt nghiệp THPT (bản sao) hoặc công chứng, Học bạ THPT (bản sao công chứng), Bằng tốt nghiệp ĐH/CĐ (bản sao) hoặc công chứng, \t\n01 bảng điểm ĐH/CĐ (bản sao) hoặc công chứng + 01 bảng photo', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ']</t>
+    <t>Khi nhập học cần chuẩn bị những giấy tờ gì vậy ạ?</t>
   </si>
   <si>
     <t>Hồ sơ nhập học bao gồm Phiếu đăng ký xét tuyển và tờ lý lịch, Giấy khai sinh (bản sao) hoặc công chứng, 2 ảnh 3x4, Bằng tốt nghiệp THPT (bản sao) hoặc công chứng, Học bạ THPT (bản sao công chứng), Bằng tốt nghiệp ĐH/CĐ (bản sao) hoặc công chứng, 01 bảng điểm ĐH/CĐ (bản sao) hoặc công chứng + 01 bảng photo.</t>
@@ -179,35 +210,44 @@
     <t>Hồ sơ nhập học gồm: Phiếu đăng ký xét tuyển và tờ lý lịch; Giấy khai sinh (bản sao hoặc công chứng); 2 ảnh 3x4; Bằng tốt nghiệp THPT (bản sao hoặc công chứng); Học bạ THPT (bản sao công chứng); Bằng tốt nghiệp ĐH/CĐ (bản sao hoặc công chứng); 01 bảng điểm ĐH/CĐ (bản sao hoặc công chứng) + 01 bảng photo.</t>
   </si>
   <si>
+    <t>['Q: Hồ sơ cần chuẩn bị những giấy tờ gì để nhập học\nA: Hồ sơ nhập học bao gồm Phiếu đăng ký xét tuyển và tờ lý lịch, Giấy khai sinh (bản sao) hoặc công chứng, 2 ảnh 3x4, \t\nBằng tốt nghiệp THPT (bản sao) hoặc công chứng, Học bạ THPT (bản sao công chứng), Bằng tốt nghiệp ĐH/CĐ (bản sao) hoặc công chứng, \t\n01 bảng điểm ĐH/CĐ (bản sao) hoặc công chứng + 01 bảng photo', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Em có thể tìm kiếm thông tin hướng dẫn nhập học ở đâu?\nA: Bạn có thể xem hướng dẫn nhập học ở đây: https://hcmut.edu.vn/tuyen-sinh/dai-hoc-chinh-quy/thong-tin-nhap-hoc', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh']</t>
+  </si>
+  <si>
     <t>0.8249784321022673</t>
   </si>
   <si>
-    <t>['Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Chương trình tiên tiến Khóa học Máy tính khác gì so với chương trình thường?\nA: Chương trình Tiên tiến ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM được đào tạo hoàn toàn bằng tiếng Anh. Giáo trình được chuyển giao từ Đại học Illinois Urbana Champaign (Mỹ) và cải tiến. Học phí khoảng 40 triệu đồng/học kỳ. Chương trình này có chuẩn tiếng Anh đầu vào là IELTS (Academic) ≥ 6.0 / TOEFL iBT ≥ 79/ TOEIC Nghe - Đọc ≥ 730 &amp; Nói - Viết ≥ 280.', 'Q: Hãy kể tên các chương trình học bổng du học - chương trình trao đổi của trường \nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và trao đổi du học hấp dẫn cho sinh viên, bao gồm:Học bổng trao đổi và học bổng toàn phần Sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc),...Chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp, mang lại cơ hội học tập và trải nghiệm tại nước ngoài.Cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp,Chương trình Việt Pháp (PFIEV) cung cấp cơ hội học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp,Những chương trình này không chỉ hỗ trợ tài chính mà còn mở rộng cơ hội phát triển kỹ năng, kiến thức và kinh nghiệm quốc tế cho sinh viên.', 'Q: Hãy kể tên các chương trình học bổng tài trợ của trường.\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và hỗ trợ tài chính cho sinh viên, bao gồm:Học bổng khuyến khích học tập từ quỹ học phí (8% quỹ học phí),Học bổng từ các doanh nghiệp, tổ chức và cá nhân như: Uster AG, Groz-Beckert AG, Nguyễn Văn Lân, BKACE, VIETCHEM, Acecook Việt Nam,Học bổng trao đổi và học bổng toàn phần Sau đại học từ các trường đại học đối tác quốc tế,\nChương trình vay ưu đãi với lãi suất 0% từ ĐHQG-HCM, Chương trình Bảo lãnh vay và hỗ trợ lãi suất từ Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Học phí trung bình mỗi học kỳ của trường là bao nhiêu\nA: Đối với năm học 2023-2024, học phí trung bình của hệ đại trà là 30 triệu/năm học, còn đối với hệ tiên tiến là 80 triệu/năm học']</t>
-  </si>
-  <si>
-    <t>Học phí chương trình PFIEV khoảng 15 triệu đồng/học kỳ, chương trình CTTA khoảng 40 triệu đồng/học kỳ.</t>
+    <t>Học phí một học kỳ của chương trình Kỹ sư Chất lượng cao Việt-Pháp (PFIEV) và chương trình Dạy và học bằng tiếng Anh (CTTA) là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Học phí một học kỳ của chương trình PFIEV là khoảng 15 triệu đồng và chương trình CTTA là khoảng 40 triệu đồng.</t>
   </si>
   <si>
     <t>Học phí của chương trình PFIEV là khoảng 15 triệu đồng/học kỳ, và chương trình Dạy và học bằng tiếng Anh (CTTA) là khoảng 40 triệu đồng/học kỳ.</t>
   </si>
   <si>
+    <t>['Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Hãy kể tên các chương trình học bổng du học - chương trình trao đổi của trường \nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và trao đổi du học hấp dẫn cho sinh viên, bao gồm:Học bổng trao đổi và học bổng toàn phần Sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc),...Chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp, mang lại cơ hội học tập và trải nghiệm tại nước ngoài.Cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp,Chương trình Việt Pháp (PFIEV) cung cấp cơ hội học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp,Những chương trình này không chỉ hỗ trợ tài chính mà còn mở rộng cơ hội phát triển kỹ năng, kiến thức và kinh nghiệm quốc tế cho sinh viên.', 'Q: Chương trình tiên tiến Khóa học Máy tính khác gì so với chương trình thường?\nA: Chương trình Tiên tiến ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM được đào tạo hoàn toàn bằng tiếng Anh. Giáo trình được chuyển giao từ Đại học Illinois Urbana Champaign (Mỹ) và cải tiến. Học phí khoảng 40 triệu đồng/học kỳ. Chương trình này có chuẩn tiếng Anh đầu vào là IELTS (Academic) ≥ 6.0 / TOEFL iBT ≥ 79/ TOEIC Nghe - Đọc ≥ 730 &amp; Nói - Viết ≥ 280.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957']</t>
+  </si>
+  <si>
     <t>0.8486486833904467</t>
   </si>
   <si>
-    <t>['Q: Chương trình tiên tiến Khóa học Máy tính khác gì so với chương trình thường?\nA: Chương trình Tiên tiến ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM được đào tạo hoàn toàn bằng tiếng Anh. Giáo trình được chuyển giao từ Đại học Illinois Urbana Champaign (Mỹ) và cải tiến. Học phí khoảng 40 triệu đồng/học kỳ. Chương trình này có chuẩn tiếng Anh đầu vào là IELTS (Academic) ≥ 6.0 / TOEFL iBT ≥ 79/ TOEIC Nghe - Đọc ≥ 730 &amp; Nói - Viết ≥ 280.', 'Q: Điều kiện để chuyển từ chương trình thường sang chương trình tiên tiến?\nA: Chương trình Tiên tiến tại Trường Đại học Bách khoa - ĐHQG-HCM có chuẩn tiếng Anh đầu vào là IELTS (Academic) ≥ 6.0 / TOEFL iBT ≥ 79/ TOEIC Nghe - Đọc ≥ 730 &amp; Nói - Viết ≥ 280. Liên hệ phòng Đào tạo để biết điều kiện cụ thể.', 'Q: Điểm chuẩn ngành Khoa học Máy tính các năm gần đây như thế nào?\nA: Điểm chuẩn ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM trong các năm gần đây có sự biến động. Cụ thể, điểm chuẩn của ngành này trong năm 2025 là 85.41 cho chương trình chính quy và 72.90 cho chương trình liên kết quốc tế với Úc, New Zealand, Mỹ.', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.', 'Q: Câu lạc bộ lập trình hoặc AI của khoa CSE tên là gì?\nA: Sinh viên ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM có cơ hội tham gia các hoạt động nghiên cứu khoa học và các câu lạc bộ chuyên môn. Tuy nhiên, tôi không có thông tin cụ thể về tên của câu lạc bộ lập trình hoặc AI của khoa CSE.']</t>
-  </si>
-  <si>
-    <t>Chương trình Tiên tiến ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM được đào tạo hoàn toàn bằng tiếng Anh, giáo trình chuyển giao từ Đại học Illinois Urbana Champaign (Mỹ) và cải tiến. Học phí khoảng 40 triệu đồng/học kỳ.
-Yêu cầu tiếng Anh đầu vào cho chương trình Tiên tiến là: IELTS (Academic) ≥ 6.0 / TOEFL iBT ≥ 79/ TOEIC Nghe - Đọc ≥ 730 &amp; Nói - Viết ≥ 280.</t>
+    <t>Chương trình Tiên tiến ngành KHMT khác gì so với chương trình thường, và yêu cầu tiếng Anh đầu vào là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Chương trình Tiên tiến ngành Khoa học Máy tính tại HCMUT được đào tạo hoàn toàn bằng tiếng Anh, giáo trình chuyển giao từ Đại học Illinois Urbana Champaign (Mỹ) và cải tiến. Học phí khoảng 40 triệu đồng/học kỳ.
+Yêu cầu tiếng Anh đầu vào của chương trình Tiên tiến là: IELTS (Academic) ≥ 6.0 / TOEFL iBT ≥ 79/ TOEIC Nghe - Đọc ≥ 730 &amp; Nói - Viết ≥ 280.</t>
   </si>
   <si>
     <t>Chương trình Tiên tiến ngành Khoa học Máy tính được đào tạo hoàn toàn bằng tiếng Anh, giáo trình chuyển giao từ Đại học Illinois Urbana Champaign (Mỹ). Học phí khoảng 40 triệu đồng/học kỳ. Yêu cầu tiếng Anh đầu vào: IELTS (Academic) ≥ 6.0 hoặc TOEFL iBT ≥ 79 hoặc TOEIC Nghe-Đọc ≥ 730 &amp; Nói-Viết ≥ 280.</t>
   </si>
   <si>
+    <t>['Q: Chương trình tiên tiến Khóa học Máy tính khác gì so với chương trình thường?\nA: Chương trình Tiên tiến ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM được đào tạo hoàn toàn bằng tiếng Anh. Giáo trình được chuyển giao từ Đại học Illinois Urbana Champaign (Mỹ) và cải tiến. Học phí khoảng 40 triệu đồng/học kỳ. Chương trình này có chuẩn tiếng Anh đầu vào là IELTS (Academic) ≥ 6.0 / TOEFL iBT ≥ 79/ TOEIC Nghe - Đọc ≥ 730 &amp; Nói - Viết ≥ 280.', 'Q: Điều kiện để chuyển từ chương trình thường sang chương trình tiên tiến?\nA: Chương trình Tiên tiến tại Trường Đại học Bách khoa - ĐHQG-HCM có chuẩn tiếng Anh đầu vào là IELTS (Academic) ≥ 6.0 / TOEFL iBT ≥ 79/ TOEIC Nghe - Đọc ≥ 730 &amp; Nói - Viết ≥ 280. Liên hệ phòng Đào tạo để biết điều kiện cụ thể.', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ']</t>
+  </si>
+  <si>
     <t>0.7203361772807358</t>
   </si>
   <si>
-    <t>['Q: Trường có ký túc xá cho sinh viên không ạ\nA: Trường chúng tôi có kí túc xá giành riêng cho sinh viên bách khoa ở số 497 Hòa Hảo, Phường 7, Quận 10, Tp. Hồ Chí Minh. Còn nếu bạn học ở cơ sở 2 thì hoàn toàn có thể ở kí túc xá đại học quốc gia.', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ']</t>
+    <t>Trường Bách khoa có ký túc xá không, và ở địa chỉ nào?</t>
   </si>
   <si>
     <t>Trường có ký túc xá giành riêng cho sinh viên Bách khoa ở số 497 Hòa Hảo, Phường 7, Quận 10, Tp. Hồ Chí Minh. Nếu bạn học ở cơ sở 2 thì có thể ở ký túc xá đại học quốc gia.</t>
@@ -216,10 +256,13 @@
     <t>Có. Ký túc xá Bách khoa dành riêng cho sinh viên tại 497 Hòa Hảo, Phường 7, Quận 10, TP.HCM, sức chứa hơn 1.800 sinh viên. Sinh viên học tại cơ sở 2 có thể ở ký túc xá ĐHQG-HCM tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM, sức chứa hơn 40.000 sinh viên.</t>
   </si>
   <si>
+    <t>['Q: Trường có ký túc xá cho sinh viên không ạ\nA: Trường chúng tôi có kí túc xá giành riêng cho sinh viên bách khoa ở số 497 Hòa Hảo, Phường 7, Quận 10, Tp. Hồ Chí Minh. Còn nếu bạn học ở cơ sở 2 thì hoàn toàn có thể ở kí túc xá đại học quốc gia.', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Địa chỉ email của trường là gì?\nA: Địa chỉ email của Trường Đại học Bách khoa - ĐHQG-HCM là info@hcmut.edu.vn.']</t>
+  </si>
+  <si>
     <t>0.781308541141866</t>
   </si>
   <si>
-    <t>['Q: Thời gian hoạt động của thư viện trường là khi nào\nA: Thư viện của trường chúng tôi hoạt động vào từ thứ hai đến thứ sáu: 7h30 - 20h00, thứ bảy: 7h30-17h00, chủ nhật và ngày lễ: nghỉ.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ']</t>
+    <t>Thư viện trường mở cửa mấy giờ và nghỉ ngày nào trong tuần?</t>
   </si>
   <si>
     <t>Thư viện trường hoạt động từ thứ hai đến thứ sáu: 7h30 - 20h00, thứ bảy: 7h30-17h00, chủ nhật và ngày lễ: nghỉ.</t>
@@ -228,58 +271,73 @@
     <t>Thư viện mở cửa từ thứ Hai đến thứ Sáu: 7h30–20h00; thứ Bảy: 7h30–17h00; Chủ nhật và ngày lễ: nghỉ.</t>
   </si>
   <si>
+    <t>['Q: Thời gian hoạt động của thư viện trường là khi nào\nA: Thư viện của trường chúng tôi hoạt động vào từ thứ hai đến thứ sáu: 7h30 - 20h00, thứ bảy: 7h30-17h00, chủ nhật và ngày lễ: nghỉ.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.']</t>
+  </si>
+  <si>
     <t>0.8338054099852454</t>
   </si>
   <si>
-    <t>['Q: Có bao nhiêu tuyến xe buýt giữa 2 cơ sở của trường?\nA: Có 2 tuyến xe buýt để di chuyển giữa 2 cơ sở là tuyến 50 và 8', 'Q: Cơ sở 2 của trường có bao nhiêu tòa?\nA: Hiện cơ sở 2 của trường gồm 4 tòa: BK-B1, BK-B2, BK-B3, BK-B6', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.', 'Q: Trường có ký túc xá cho sinh viên không ạ\nA: Trường chúng tôi có kí túc xá giành riêng cho sinh viên bách khoa ở số 497 Hòa Hảo, Phường 7, Quận 10, Tp. Hồ Chí Minh. Còn nếu bạn học ở cơ sở 2 thì hoàn toàn có thể ở kí túc xá đại học quốc gia.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957']</t>
-  </si>
-  <si>
-    <t>Cơ sở 2 của trường có 4 tòa: BK-B1, BK-B2, BK-B3, BK-B6. Có 2 tuyến xe buýt để di chuyển giữa 2 cơ sở là tuyến 50 và 8.</t>
+    <t>Cơ sở 2 của trường có bao nhiêu tòa nhà và có những tuyến xe buýt nào để đi lại giữa hai cơ sở?</t>
+  </si>
+  <si>
+    <t>Hiện cơ sở 2 của trường gồm 4 tòa: BK-B1, BK-B2, BK-B3, BK-B6. Có 2 tuyến xe buýt để di chuyển giữa 2 cơ sở là tuyến 50 và 8.</t>
   </si>
   <si>
     <t>Cơ sở 2 gồm 4 tòa: BK-B1, BK-B2, BK-B3, BK-B6. Có 2 tuyến xe buýt để di chuyển giữa 2 cơ sở là tuyến 50 và tuyến 8.</t>
   </si>
   <si>
+    <t>['Q: Cơ sở 2 của trường có bao nhiêu tòa?\nA: Hiện cơ sở 2 của trường gồm 4 tòa: BK-B1, BK-B2, BK-B3, BK-B6', 'Q: Có bao nhiêu tuyến xe buýt giữa 2 cơ sở của trường?\nA: Có 2 tuyến xe buýt để di chuyển giữa 2 cơ sở là tuyến 50 và 8', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957']</t>
+  </si>
+  <si>
     <t>0.8561626229165428</t>
   </si>
   <si>
-    <t>['Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Làm sao để liên hệ trực tiếp với khoa Khoa học Máy tính?\nA: Để liên hệ trực tiếp với Khoa Khoa học và Kỹ thuật Máy tính (CSE) tại Trường Đại học Bách khoa - ĐHQG-HCM, bạn có thể tìm thông tin liên lạc từ Trưởng khoa hoặc các Phó Trưởng khoa. Trưởng khoa hiện tại là PGS. TS. Quản Thành Thơ với email qttho@hcmut.edu.vn.', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ']</t>
-  </si>
-  <si>
-    <t>Hiệu trưởng hiện tại của trường là PGS. TS. Mai Thanh Phong.</t>
+    <t>Hiệu trưởng hiện tại của Trường Đại học Bách khoa TP.HCM là ai?</t>
+  </si>
+  <si>
+    <t>Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong.</t>
   </si>
   <si>
     <t>Hiệu trưởng hiện tại là PGS. TS. Mai Thanh Phong, được bổ nhiệm vào tháng 5 năm 2018.</t>
   </si>
   <si>
+    <t>['Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Làm sao để liên hệ trực tiếp với khoa Khoa học Máy tính?\nA: Để liên hệ trực tiếp với Khoa Khoa học và Kỹ thuật Máy tính (CSE) tại Trường Đại học Bách khoa - ĐHQG-HCM, bạn có thể tìm thông tin liên lạc từ Trưởng khoa hoặc các Phó Trưởng khoa. Trưởng khoa hiện tại là PGS. TS. Quản Thành Thơ với email qttho@hcmut.edu.vn.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.']</t>
+  </si>
+  <si>
     <t>0.7247792189489201</t>
   </si>
   <si>
-    <t>['Q: Cơ cấu của trường hiện tại như thế nào? \nA: Hiện trường đang quản lý 12 Khoa/Trung tâm đào tạo, đào tạo 40 ngành bậc Đại học, 34 ngành bậc Thạc sĩ, 32 ngành bậc Tiến sĩ [2] với tổng số hơn 23.000 sinh viên, trên 2.100 học viên cao học và gần 300 nghiên cứu sinh.', 'Q: Trường mình có bao nhiêu ngành tất cả\n\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có tổng cộng 40 ngành và hơn 60 chuyên ngành đào tạo cho sinh viên.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu']</t>
-  </si>
-  <si>
-    <t>Hiện trường đang quản lý 12 Khoa/Trung tâm đào tạo với tổng số hơn 23.000 sinh viên và trên 2.100 học viên cao học.</t>
+    <t>Cơ cấu đào tạo hiện tại của trường gồm bao nhiêu khoa và tổng số lượng sinh viên, học viên cao học là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Hiện trường đang quản lý 12 Khoa/Trung tâm đào tạo, đào tạo với tổng số hơn 23.000 sinh viên và trên 2.100 học viên cao học.</t>
   </si>
   <si>
     <t>Hiện trường đang quản lý 12 Khoa/Trung tâm đào tạo, với tổng số hơn 23.000 sinh viên, trên 2.100 học viên cao học và gần 300 nghiên cứu sinh.</t>
   </si>
   <si>
+    <t>['Q: Cơ cấu của trường hiện tại như thế nào? \nA: Hiện trường đang quản lý 12 Khoa/Trung tâm đào tạo, đào tạo 40 ngành bậc Đại học, 34 ngành bậc Thạc sĩ, 32 ngành bậc Tiến sĩ [2] với tổng số hơn 23.000 sinh viên, trên 2.100 học viên cao học và gần 300 nghiên cứu sinh.', 'Q: Trường mình có bao nhiêu ngành tất cả\n\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có tổng cộng 40 ngành và hơn 60 chuyên ngành đào tạo cho sinh viên.', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.']</t>
+  </si>
+  <si>
     <t>0.8215649085928651</t>
   </si>
   <si>
-    <t>['Q: Để tốt nghiệp em cần tích lũy bao nhiêu tín chỉ\nA: Để tốt nghiệp, sinh viên cần đạt đủ số tín chỉ yêu cầu ở mỗi khoa. Trung bình tổng số tín chỉ là 142 tín', 'Q: Thời gian đào tạo 1 học kỳ chính của trường kéo dài trong bao lâu\nA: Một học kỳ chính tại trường thường kéo dài 15 tuần học và 2 tuần thi', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Trường có bao nhiêu kỳ học chính?\nA: Trường chúng tôi có 2 kỳ học chính và 1 kỳ học hè', 'Q: Hãy kể tên các chương trình học bổng du học - chương trình trao đổi của trường \nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và trao đổi du học hấp dẫn cho sinh viên, bao gồm:Học bổng trao đổi và học bổng toàn phần Sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc),...Chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp, mang lại cơ hội học tập và trải nghiệm tại nước ngoài.Cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp,Chương trình Việt Pháp (PFIEV) cung cấp cơ hội học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp,Những chương trình này không chỉ hỗ trợ tài chính mà còn mở rộng cơ hội phát triển kỹ năng, kiến thức và kinh nghiệm quốc tế cho sinh viên.']</t>
-  </si>
-  <si>
-    <t>Một học kỳ chính tại trường kéo dài 15 tuần học và 2 tuần thi. Sinh viên cần tích lũy trung bình tổng cộng 142 tín chỉ để tốt nghiệp.</t>
+    <t>Một học kỳ chính ở Bách khoa kéo dài bao nhiêu tuần và sinh viên cần tích lũy bao nhiêu tín chỉ để tốt nghiệp?</t>
+  </si>
+  <si>
+    <t>Một học kỳ chính tại trường kéo dài 15 tuần học và 2 tuần thi. Để tốt nghiệp, sinh viên cần đạt đủ khoảng 142 tín chỉ.</t>
   </si>
   <si>
     <t>Một học kỳ chính kéo dài 15 tuần học và 2 tuần thi. Để tốt nghiệp, sinh viên cần tích lũy trung bình 142 tín chỉ.</t>
   </si>
   <si>
+    <t>['Q: Thời gian đào tạo 1 học kỳ chính của trường kéo dài trong bao lâu\nA: Một học kỳ chính tại trường thường kéo dài 15 tuần học và 2 tuần thi', 'Q: Để tốt nghiệp em cần tích lũy bao nhiêu tín chỉ\nA: Để tốt nghiệp, sinh viên cần đạt đủ số tín chỉ yêu cầu ở mỗi khoa. Trung bình tổng số tín chỉ là 142 tín', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957']</t>
+  </si>
+  <si>
     <t>0.8073331236890077</t>
   </si>
   <si>
-    <t>['Q: Điểm đạt để qua môn tại trường là bao nhiêu?\nA: Điểm đạt để qua môn ở tường là điểm D trở lên tức điểm 4 trên thang điểm 10', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ']</t>
+    <t>Điểm tối thiểu để qua môn tại Bách khoa là bao nhiêu?</t>
   </si>
   <si>
     <t>Điểm đạt để qua môn ở trường là điểm D trở lên tức điểm 4 trên thang điểm 10.</t>
@@ -288,10 +346,13 @@
     <t>Điểm đạt để qua môn là điểm D trở lên, tức điểm 4 trên thang điểm 10.</t>
   </si>
   <si>
+    <t>['Q: Điểm đạt để qua môn tại trường là bao nhiêu?\nA: Điểm đạt để qua môn ở tường là điểm D trở lên tức điểm 4 trên thang điểm 10', 'Q: Phương thức xét tuyển tổng hợp tính điểm như thế nào?\nA: Phương thức xét tuyển tổng hợp của Trường Đại học Bách khoa - ĐHQG-HCM tính điểm dựa trên công thức sau:[Điểm Xét tuyển] = [Điểm học lực] + [Điểm ưu tiên] (Thang điểm 100)Trong đó:[Điểm học lực] = [Điểm năng lực] × 70% + [Điểm TNTHPTquy đổi] × 20% + [Điểm học THPTquy đổi] × 10% (Thang điểm 100)Tùy thuộc vào đối tượng xét tuyển, các thành phần điểm sẽ được tính khác nhau. Ví dụ, đối với thí sinh có kết quả thi Đánh giá Năng lực ĐHQG-HCM, điểm năng lực được tính dựa trên điểm thi này.', 'Q: Thông tin về kí túc xá cũng như cơ sở vật chất của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp cho sinh viên các cơ sở vật chất hiện đại, bao gồm:Ký túc xá:- Ký túc xá Bách khoa: Sức chứa hơn 1.800 sinh viên, địa chỉ tại 497 Đường Hòa Hảo, Phường Diên Hồng, TP.HCM.- Ký túc xá ĐHQG-HCM: Sức chứa hơn 40.000 sinh viên, địa chỉ tại Đường Tạ Quang Bửu, Khu phố 33, Phường Linh Xuân, TP.HCM.Cơ sở vật chất:- Cơ sở 1: Rộng 14 ha, tại 268 Lý Thường Kiệt, Phường Diên Hồng, TP.HCM.- Cơ sở 2: Rộng 26 ha, tại Khu phố Tân Lập, Phường Đông Hòa, TP.HCM.- Phòng thí nghiệm/xưởng thực hành: Hơn 164 phòng thí nghiệm, xưởng thực hành.- Phòng thí nghiệm trọng điểm: 2 phòng thí nghiệm trọng điểm quốc gia, 5 phòng thí nghiệm trọng điểm ĐHQG-HCM.- Cơ sở vật chất thể thao: Nhà thi đấu thể thao đa năng, sân bóng đá ngoài trời/trong nhà (futsal), bóng rổ, bóng chuyền, bóng bàn, tennis, pickleball ở cả 2 cơ sở.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Điểm chuẩn ngành Khoa học Máy tính các năm gần đây như thế nào?\nA: Điểm chuẩn ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM trong các năm gần đây có sự biến động. Cụ thể, điểm chuẩn của ngành này trong năm 2025 là 85.41 cho chương trình chính quy và 72.90 cho chương trình liên kết quốc tế với Úc, New Zealand, Mỹ.']</t>
+  </si>
+  <si>
     <t>0.8018799813471732</t>
   </si>
   <si>
-    <t>['Q: Sinh viên có thể nộp hồ sơ để hưởng chế độ miễn giảm học phí của trường ở đâu?\nA: Sinh viên có thể nộp hồ sơ trực tiếp tại phòng Công tác sinh viên', 'Q: Các đối tượng sinh viên được hưởng chế độ miễn giảm học phí là gì?\nA: Các đối tượng được hưởng chế độ miễn giảm học phí là: SV là con của người có công với cách mạng, SV khuyết tật, SV mồ côi cả cha lẫn mẹ, SV là người dân tộc thiểu số (DTTS) thuộc hộ nghèo/cận nghèo, SV là người DTTS rất ít người ở vùng có điều kiện Kinh tế -Xã hội khó khăn, SV là người DTTS  ít người ở vùng có điều kiện Kinh tế - Xã hội đặc biệt khó khăn, SV có cha/mẹ bị tai nạn lao động hoặc mắc bệnh nghề nghiệp được hưởng trợ cấp thường xuyên.', 'Q: Trường có chế độ miễn, giảm học phí không?\nA: Có, trường có chế độ miễn, giảm học phí cho sinh viên ở nhiều trường hợp.', 'Q: Có wifi miễn phí cho sinh viên không?\nA: Trường Đại học Bách khoa - ĐHQG-HCM có cung cấp wifi cho sinh viên.', 'Q: Trường có ký túc xá cho sinh viên không ạ\nA: Trường chúng tôi có kí túc xá giành riêng cho sinh viên bách khoa ở số 497 Hòa Hảo, Phường 7, Quận 10, Tp. Hồ Chí Minh. Còn nếu bạn học ở cơ sở 2 thì hoàn toàn có thể ở kí túc xá đại học quốc gia.']</t>
+    <t>Em thuộc diện hộ nghèo là người dân tộc thiểu số, vậy có được miễn giảm học phí không và nộp hồ sơ ở đâu?</t>
   </si>
   <si>
     <t>Có, sinh viên là người dân tộc thiểu số thuộc hộ nghèo được hưởng chế độ miễn giảm học phí. Bạn có thể nộp hồ sơ trực tiếp tại phòng Công tác sinh viên.</t>
@@ -300,38 +361,43 @@
     <t>Có. Sinh viên là người dân tộc thiểu số thuộc hộ nghèo/cận nghèo thuộc diện được hưởng chế độ miễn giảm học phí của trường. Bạn nộp hồ sơ trực tiếp tại Phòng Công tác Sinh viên.</t>
   </si>
   <si>
+    <t>['Q: Các đối tượng sinh viên được hưởng chế độ miễn giảm học phí là gì?\nA: Các đối tượng được hưởng chế độ miễn giảm học phí là: SV là con của người có công với cách mạng, SV khuyết tật, SV mồ côi cả cha lẫn mẹ, SV là người dân tộc thiểu số (DTTS) thuộc hộ nghèo/cận nghèo, SV là người DTTS rất ít người ở vùng có điều kiện Kinh tế -Xã hội khó khăn, SV là người DTTS  ít người ở vùng có điều kiện Kinh tế - Xã hội đặc biệt khó khăn, SV có cha/mẹ bị tai nạn lao động hoặc mắc bệnh nghề nghiệp được hưởng trợ cấp thường xuyên.', 'Q: Sinh viên có thể nộp hồ sơ để hưởng chế độ miễn giảm học phí của trường ở đâu?\nA: Sinh viên có thể nộp hồ sơ trực tiếp tại phòng Công tác sinh viên', 'Q: Trường có chế độ miễn, giảm học phí không?\nA: Có, trường có chế độ miễn, giảm học phí cho sinh viên ở nhiều trường hợp.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.']</t>
+  </si>
+  <si>
     <t>0.8669441304965138</t>
   </si>
   <si>
-    <t>['Q: Em muốn hỏi về các loại học bổng mà trường đang có\nA: Trường hiện đang có 3 loại học bổng lần lượt học bổng loại I, loại II và loại III', 'Q: Hãy kể tên các chương trình học bổng du học - chương trình trao đổi của trường \nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và trao đổi du học hấp dẫn cho sinh viên, bao gồm:Học bổng trao đổi và học bổng toàn phần Sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc),...Chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp, mang lại cơ hội học tập và trải nghiệm tại nước ngoài.Cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp,Chương trình Việt Pháp (PFIEV) cung cấp cơ hội học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp,Những chương trình này không chỉ hỗ trợ tài chính mà còn mở rộng cơ hội phát triển kỹ năng, kiến thức và kinh nghiệm quốc tế cho sinh viên.', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Hãy kể tên các chương trình học bổng tài trợ của trường.\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và hỗ trợ tài chính cho sinh viên, bao gồm:Học bổng khuyến khích học tập từ quỹ học phí (8% quỹ học phí),Học bổng từ các doanh nghiệp, tổ chức và cá nhân như: Uster AG, Groz-Beckert AG, Nguyễn Văn Lân, BKACE, VIETCHEM, Acecook Việt Nam,Học bổng trao đổi và học bổng toàn phần Sau đại học từ các trường đại học đối tác quốc tế,\nChương trình vay ưu đãi với lãi suất 0% từ ĐHQG-HCM, Chương trình Bảo lãnh vay và hỗ trợ lãi suất từ Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Có wifi miễn phí cho sinh viên không?\nA: Trường Đại học Bách khoa - ĐHQG-HCM có cung cấp wifi cho sinh viên.']</t>
-  </si>
-  <si>
-    <t>Trường hiện đang có 3 loại học bổng lần lượt học bổng loại I, loại II và loại III. Ngoài ra, trường còn có học bổng khuyến khích học tập, quỹ học bổng và Hỗ trợ phát triển Bách khoa, học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp và học bổng dành cho sinh viên chương trình đào tạo quốc tế.</t>
+    <t>Trường có những loại học bổng nào dành cho sinh viên đang học?</t>
+  </si>
+  <si>
+    <t>Trường hiện đang có 3 loại học bổng lần lượt học bổng loại I, loại II và loại III. Ngoài ra, trường còn có các học bổng khuyến khích học tập, học bổng từ các doanh nghiệp, tổ chức, học bổng trao đổi và học bổng toàn phần sau đại học từ các trường đại học đối tác quốc tế, chương trình vay ưu đãi và chương trình bảo lãnh vay.</t>
   </si>
   <si>
     <t>Trường có 3 loại học bổng: học bổng loại I, loại II và loại III. Ngoài ra còn có học bổng khuyến khích học tập từ quỹ học phí (8% quỹ học phí, trị giá tới 120% học phí/học kỳ/suất), học bổng từ doanh nghiệp và tổ chức (Uster AG, Groz-Beckert AG, Acecook Việt Nam, ...), học bổng trao đổi quốc tế và chương trình vay ưu đãi 0% lãi suất từ ĐHQG-HCM.</t>
   </si>
   <si>
+    <t>['Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Hãy kể tên các chương trình học bổng du học - chương trình trao đổi của trường \nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và trao đổi du học hấp dẫn cho sinh viên, bao gồm:Học bổng trao đổi và học bổng toàn phần Sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc),...Chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp, mang lại cơ hội học tập và trải nghiệm tại nước ngoài.Cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp,Chương trình Việt Pháp (PFIEV) cung cấp cơ hội học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp,Những chương trình này không chỉ hỗ trợ tài chính mà còn mở rộng cơ hội phát triển kỹ năng, kiến thức và kinh nghiệm quốc tế cho sinh viên.', 'Q: Hãy kể tên các chương trình học bổng tài trợ của trường.\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và hỗ trợ tài chính cho sinh viên, bao gồm:Học bổng khuyến khích học tập từ quỹ học phí (8% quỹ học phí),Học bổng từ các doanh nghiệp, tổ chức và cá nhân như: Uster AG, Groz-Beckert AG, Nguyễn Văn Lân, BKACE, VIETCHEM, Acecook Việt Nam,Học bổng trao đổi và học bổng toàn phần Sau đại học từ các trường đại học đối tác quốc tế,\nChương trình vay ưu đãi với lãi suất 0% từ ĐHQG-HCM, Chương trình Bảo lãnh vay và hỗ trợ lãi suất từ Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Em muốn hỏi về các loại học bổng mà trường đang có\nA: Trường hiện đang có 3 loại học bổng lần lượt học bổng loại I, loại II và loại III', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ']</t>
+  </si>
+  <si>
     <t>0.8317565329142352</t>
   </si>
   <si>
-    <t>['Q: Hãy kể tên các chương trình học bổng du học - chương trình trao đổi của trường \nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và trao đổi du học hấp dẫn cho sinh viên, bao gồm:Học bổng trao đổi và học bổng toàn phần Sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc),...Chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp, mang lại cơ hội học tập và trải nghiệm tại nước ngoài.Cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp,Chương trình Việt Pháp (PFIEV) cung cấp cơ hội học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp,Những chương trình này không chỉ hỗ trợ tài chính mà còn mở rộng cơ hội phát triển kỹ năng, kiến thức và kinh nghiệm quốc tế cho sinh viên.', 'Q: Hãy kể tên các chương trình học bổng tài trợ của trường.\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và hỗ trợ tài chính cho sinh viên, bao gồm:Học bổng khuyến khích học tập từ quỹ học phí (8% quỹ học phí),Học bổng từ các doanh nghiệp, tổ chức và cá nhân như: Uster AG, Groz-Beckert AG, Nguyễn Văn Lân, BKACE, VIETCHEM, Acecook Việt Nam,Học bổng trao đổi và học bổng toàn phần Sau đại học từ các trường đại học đối tác quốc tế,\nChương trình vay ưu đãi với lãi suất 0% từ ĐHQG-HCM, Chương trình Bảo lãnh vay và hỗ trợ lãi suất từ Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Sinh viên nước ngoài có thể đăng ký học tại trường không?\nA: Có, liên hệ phòng Hợp tác Quốc tế', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957']</t>
-  </si>
-  <si>
-    <t>Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và trao đổi du học, bao gồm:
-*   Học bổng trao đổi và học bổng toàn phần Sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc),...
-*   Chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp.
-*   Cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp.
-*   Chương trình Việt Pháp (PFIEV) cung cấp cơ hội học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp.</t>
+    <t>Trường có chương trình trao đổi sinh viên hoặc học bổng du học nước ngoài không, cụ thể là những trường và quốc gia nào?</t>
+  </si>
+  <si>
+    <t>Trường Đại học Bách khoa TP.HCM (HCMUT) có chương trình trao đổi sinh viên và học bổng du học nước ngoài. Cụ thể, trường có trao đổi và học bổng toàn phần sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc), và chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp. Ngoài ra, còn có cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp, và chương trình Việt Pháp (PFIEV) với cơ hội học tập tại Pháp.</t>
   </si>
   <si>
     <t>Có. Trường cung cấp học bổng trao đổi và học bổng toàn phần Sau đại học tại các đối tác như University of Technology Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc). Có chương trình trao đổi với các trường tại Pháp, học bổng vùng, EIFFEL, ERASMUS, và chương trình Việt-Pháp (PFIEV) cho phép học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp.</t>
   </si>
   <si>
+    <t>['Q: Hãy kể tên các chương trình học bổng du học - chương trình trao đổi của trường \nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và trao đổi du học hấp dẫn cho sinh viên, bao gồm:Học bổng trao đổi và học bổng toàn phần Sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc),...Chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp, mang lại cơ hội học tập và trải nghiệm tại nước ngoài.Cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp,Chương trình Việt Pháp (PFIEV) cung cấp cơ hội học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp,Những chương trình này không chỉ hỗ trợ tài chính mà còn mở rộng cơ hội phát triển kỹ năng, kiến thức và kinh nghiệm quốc tế cho sinh viên.', 'Q: Hãy kể tên các chương trình học bổng tài trợ của trường.\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và hỗ trợ tài chính cho sinh viên, bao gồm:Học bổng khuyến khích học tập từ quỹ học phí (8% quỹ học phí),Học bổng từ các doanh nghiệp, tổ chức và cá nhân như: Uster AG, Groz-Beckert AG, Nguyễn Văn Lân, BKACE, VIETCHEM, Acecook Việt Nam,Học bổng trao đổi và học bổng toàn phần Sau đại học từ các trường đại học đối tác quốc tế,\nChương trình vay ưu đãi với lãi suất 0% từ ĐHQG-HCM, Chương trình Bảo lãnh vay và hỗ trợ lãi suất từ Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.']</t>
+  </si>
+  <si>
     <t>0.7794993458627993</t>
   </si>
   <si>
-    <t>['Q: Khoa điện điện tử của trường có những ngành nào\nA: Trường chúng tôi có các ngành của khoa Điện - Điện tử như: Kỹ thuật Điều khiển và Tự động hóa, Kỹ thuật Điện tử - Viễn thông, Kỹ thuật Điện, Thiết kế vi mạch, và các chương trình Song ngành như Kỹ thuật Điện tử - Viễn thông và Kỹ thuật Điện; Kỹ thuật Điện tử - Viễn thông và Kỹ thuật Điều khiển và Tự động hóa; Kỹ thuật Điện và Kỹ thuật Điện tử - Viễn thông; Kỹ thuật Điện và Kỹ thuật Điều khiển và Tự động hóa; Kỹ thuật Điều khiển và Tự động hóa và Kỹ thuật Điện tử - Viễn thông; Kỹ thuật Điều khiển và Tự động hóa và Kỹ thuật Điện. Ngoài ra, Khoa Kỹ thuật Địa chất và Dầu khí đào tạo các ngành: Địa Kỹ thuật Xây dựng, Kỹ thuật Dầu khí, và Kỹ thuật Địa chất.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.', 'Q: Trường mình có bao nhiêu ngành tất cả\n\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có tổng cộng 40 ngành và hơn 60 chuyên ngành đào tạo cho sinh viên.', 'Q: Khoa cơ khí của trường có những ngành nào\nA: Trường chúng tôi có các ngành của khoa cơ khí như: Bảo dưỡng Công nghiệp, Kỹ thuật Cơ khí,Công nghệ May,Kỹ thuật Cơ điện tử, Kỹ thuật Dệt, Kỹ thuật Hệ thống Công nghiệp, Logistics và Quản lý Chuỗi cung ứng, Kỹ thuật Nhiệt.']</t>
+    <t>Khoa Điện - Điện tử của trường đào tạo những ngành và chuyên ngành nào?</t>
   </si>
   <si>
     <t>Trường chúng tôi có các ngành của khoa Điện - Điện tử như: Kỹ thuật Điều khiển và Tự động hóa, Kỹ thuật Điện tử - Viễn thông, Kỹ thuật Điện, Thiết kế vi mạch, và các chương trình Song ngành như Kỹ thuật Điện tử - Viễn thông và Kỹ thuật Điện; Kỹ thuật Điện tử - Viễn thông và Kỹ thuật Điều khiển và Tự động hóa; Kỹ thuật Điện và Kỹ thuật Điện tử - Viễn thông; Kỹ thuật Điện và Kỹ thuật Điều khiển và Tự động hóa; Kỹ thuật Điều khiển và Tự động hóa và Kỹ thuật Điện tử - Viễn thông; Kỹ thuật Điều khiển và Tự động hóa và Kỹ thuật Điện.</t>
@@ -340,10 +406,13 @@
     <t>Khoa Điện - Điện tử đào tạo các ngành: Kỹ thuật Điều khiển và Tự động hóa, Kỹ thuật Điện tử - Viễn thông, Kỹ thuật Điện, Thiết kế vi mạch. Ngoài ra còn có nhiều chương trình Song ngành kết hợp giữa các ngành trên.</t>
   </si>
   <si>
+    <t>['Q: Khoa điện điện tử của trường có những ngành nào\nA: Trường chúng tôi có các ngành của khoa Điện - Điện tử như: Kỹ thuật Điều khiển và Tự động hóa, Kỹ thuật Điện tử - Viễn thông, Kỹ thuật Điện, Thiết kế vi mạch, và các chương trình Song ngành như Kỹ thuật Điện tử - Viễn thông và Kỹ thuật Điện; Kỹ thuật Điện tử - Viễn thông và Kỹ thuật Điều khiển và Tự động hóa; Kỹ thuật Điện và Kỹ thuật Điện tử - Viễn thông; Kỹ thuật Điện và Kỹ thuật Điều khiển và Tự động hóa; Kỹ thuật Điều khiển và Tự động hóa và Kỹ thuật Điện tử - Viễn thông; Kỹ thuật Điều khiển và Tự động hóa và Kỹ thuật Điện. Ngoài ra, Khoa Kỹ thuật Địa chất và Dầu khí đào tạo các ngành: Địa Kỹ thuật Xây dựng, Kỹ thuật Dầu khí, và Kỹ thuật Địa chất.', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.', 'Q: Trường mình có bao nhiêu ngành tất cả\n\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có tổng cộng 40 ngành và hơn 60 chuyên ngành đào tạo cho sinh viên.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Chuyên ngành Công nghệ dữ liệu và Dữ liệu lớn có gì đặc biệt?\nA: Chuyên ngành Công nghệ Dữ liệu và Dữ liệu lớn tại Trường Đại học Bách khoa - ĐHQG-HCM là một chương trình đào tạo tiên tiến, tập trung vào việc trang bị cho sinh viên kiến thức và kỹ năng về xử lý, phân tích và ứng dụng dữ liệu lớn. Chương trình này giúp sinh viên có khả năng làm việc với các công nghệ dữ liệu hiện đại, đáp ứng nhu cầu của thị trường lao động trong lĩnh vực công nghệ thông tin. Sinh viên theo học chuyên ngành này sẽ được học về các kỹ thuật xử lý dữ liệu, khai thác dữ liệu, và ứng dụng trí tuệ nhân tạo trong phân tích dữ liệu. Với kiến thức và kỹ năng chuyên sâu, sinh viên tốt nghiệp có thể đảm nhận các vị trí như Kỹ sư dữ liệu, Nhà phân tích dữ liệu, và Chuyên viên phân tích kinh doanh tại các doanh nghiệp công nghệ, tài chính, và nhiều lĩnh vực khác.']</t>
+  </si>
+  <si>
     <t>0.8382174426470018</t>
   </si>
   <si>
-    <t>['Q: Khoa kỹ thuật giao thông của trường có những ngành nào\nA: Trường chúng tôi có các ngành của khoa Kỹ thuật Giao thông như Kỹ thuật Hàng không, Kỹ thuật Ô tô, Kỹ thuật Tàu thủy, và chương trình Song ngành Kỹ thuật Tàu thủy - Hàng không.', 'Q: Khoa kỹ thuật xây dựng của trường có những ngành nào\nA: Trường chúng tôi có các ngành của khoa kỹ thuật xây dựng như: Kỹ thuật Xây dựng Công trình biển, Kỹ thuật Cơ sở hạ tầng, Công nghệ Kỹ thuật Vật liệu Xây dựng, Kỹ thuật Công trình Xây dựng, Kiến trúc, Kỹ thuật Trắc địa - Bản đồ, Kỹ thuật Công trình Thủy, Kỹ thuật Xây dựng Công trình Giao thông, và Kinh tế Xây dựng.', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.', 'Q: Khoa điện điện tử của trường có những ngành nào\nA: Trường chúng tôi có các ngành của khoa Điện - Điện tử như: Kỹ thuật Điều khiển và Tự động hóa, Kỹ thuật Điện tử - Viễn thông, Kỹ thuật Điện, Thiết kế vi mạch, và các chương trình Song ngành như Kỹ thuật Điện tử - Viễn thông và Kỹ thuật Điện; Kỹ thuật Điện tử - Viễn thông và Kỹ thuật Điều khiển và Tự động hóa; Kỹ thuật Điện và Kỹ thuật Điện tử - Viễn thông; Kỹ thuật Điện và Kỹ thuật Điều khiển và Tự động hóa; Kỹ thuật Điều khiển và Tự động hóa và Kỹ thuật Điện tử - Viễn thông; Kỹ thuật Điều khiển và Tự động hóa và Kỹ thuật Điện. Ngoài ra, Khoa Kỹ thuật Địa chất và Dầu khí đào tạo các ngành: Địa Kỹ thuật Xây dựng, Kỹ thuật Dầu khí, và Kỹ thuật Địa chất.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957']</t>
+    <t>Khoa Kỹ thuật Giao thông đào tạo những ngành nào vậy ạ?</t>
   </si>
   <si>
     <t>Trường chúng tôi có các ngành của khoa Kỹ thuật Giao thông như Kỹ thuật Hàng không, Kỹ thuật Ô tô, Kỹ thuật Tàu thủy, và chương trình Song ngành Kỹ thuật Tàu thủy - Hàng không.</t>
@@ -352,35 +421,44 @@
     <t>Khoa Kỹ thuật Giao thông đào tạo các ngành: Kỹ thuật Hàng không, Kỹ thuật Ô tô, Kỹ thuật Tàu thủy, và chương trình Song ngành Kỹ thuật Tàu thủy - Hàng không.</t>
   </si>
   <si>
+    <t>['Q: Khoa kỹ thuật giao thông của trường có những ngành nào\nA: Trường chúng tôi có các ngành của khoa Kỹ thuật Giao thông như Kỹ thuật Hàng không, Kỹ thuật Ô tô, Kỹ thuật Tàu thủy, và chương trình Song ngành Kỹ thuật Tàu thủy - Hàng không.', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.', 'Q: Khoa kỹ thuật xây dựng của trường có những ngành nào\nA: Trường chúng tôi có các ngành của khoa kỹ thuật xây dựng như: Kỹ thuật Xây dựng Công trình biển, Kỹ thuật Cơ sở hạ tầng, Công nghệ Kỹ thuật Vật liệu Xây dựng, Kỹ thuật Công trình Xây dựng, Kiến trúc, Kỹ thuật Trắc địa - Bản đồ, Kỹ thuật Công trình Thủy, Kỹ thuật Xây dựng Công trình Giao thông, và Kinh tế Xây dựng.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Khoa điện điện tử của trường có những ngành nào\nA: Trường chúng tôi có các ngành của khoa Điện - Điện tử như: Kỹ thuật Điều khiển và Tự động hóa, Kỹ thuật Điện tử - Viễn thông, Kỹ thuật Điện, Thiết kế vi mạch, và các chương trình Song ngành như Kỹ thuật Điện tử - Viễn thông và Kỹ thuật Điện; Kỹ thuật Điện tử - Viễn thông và Kỹ thuật Điều khiển và Tự động hóa; Kỹ thuật Điện và Kỹ thuật Điện tử - Viễn thông; Kỹ thuật Điện và Kỹ thuật Điều khiển và Tự động hóa; Kỹ thuật Điều khiển và Tự động hóa và Kỹ thuật Điện tử - Viễn thông; Kỹ thuật Điều khiển và Tự động hóa và Kỹ thuật Điện. Ngoài ra, Khoa Kỹ thuật Địa chất và Dầu khí đào tạo các ngành: Địa Kỹ thuật Xây dựng, Kỹ thuật Dầu khí, và Kỹ thuật Địa chất.']</t>
+  </si>
+  <si>
     <t>0.8576278198278937</t>
   </si>
   <si>
-    <t>['Q: Ngành Khoa học máy tính sẽ học những môn gì chủ yếu\nA: Môn cơ sở ngành của ngành khoa học máy tính trường chúng tôi là: nhập môn điện toán, cấu trúc rời rạc, hệ thống số, kĩ thuật lập trình, cấu trúc dữ liệu và giải thuật, kiến trúc máy tính, mô hình hóa toán học, hệ điều hành, mạng máy tính, công nghệ phần mềm, lập trình nâng cao, hệ cơ sở và dữ liệu, nguyên lý ngôn ngữ lập trình. ', 'Q: Học ngành Khoa học máy tính ra có thể làm việc ở đâu\nA: Ngành khoa học máy tính của trường chúng tôi có các chuyên ngành như: Khoa học Máy tính, Công nghệ dữ liệu và dữ liệu lớn, Công nghệ Phần mềm, An ninh hệ thống và mạng, Trí tuệ nhân tạo,Công nghệ Thông tin. Các công ty công nghệ, ngân hàng, công ty tài chính, thương mại điện tử, các doanh nghiệp sản xuất, và thậm chí cả các cơ quan nhà nước đều có nhu cầu rất lớn về nhân lực khoa học máy tính.', 'Q: Câu lạc bộ lập trình hoặc AI của khoa CSE tên là gì?\nA: Sinh viên ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM có cơ hội tham gia các hoạt động nghiên cứu khoa học và các câu lạc bộ chuyên môn. Tuy nhiên, tôi không có thông tin cụ thể về tên của câu lạc bộ lập trình hoặc AI của khoa CSE.', 'Q: Chuyên ngành Trí tuệ nhân tạo của khoa CSE học những gì?\nA: Chuyên ngành Trí tuệ Nhân tạo của Khoa Khoa học và Kỹ thuật Máy tính (CSE) tại Trường Đại học Bách khoa - ĐHQG-HCM trang bị cho sinh viên kiến thức và kỹ năng về trí tuệ nhân tạo, bao gồm các lĩnh vực như học máy, xử lý ngôn ngữ tự nhiên, thị giác máy tính, và robot thông minh. Sinh viên sẽ được học cách thiết kế, xây dựng và triển khai các hệ thống thông minh, ứng dụng trong nhiều lĩnh vực khác nhau.', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu']</t>
+    <t>Ngành Khoa học Máy tính học những môn cơ sở ngành gì và sau khi ra trường có thể làm ở đâu?</t>
   </si>
   <si>
     <t>Môn cơ sở ngành của ngành Khoa học máy tính trường chúng tôi là: nhập môn điện toán, cấu trúc rời rạc, hệ thống số, kĩ thuật lập trình, cấu trúc dữ liệu và giải thuật, kiến trúc máy tính, mô hình hóa toán học, hệ điều hành, mạng máy tính, công nghệ phần mềm, lập trình nâng cao, hệ cơ sở và dữ liệu, nguyên lý ngôn ngữ lập trình.
-Sau khi ra trường, bạn có thể làm việc tại các công ty công nghệ, ngân hàng, công ty tài chính, thương mại điện tử, các doanh nghiệp sản xuất, và thậm chí cả các cơ quan nhà nước.</t>
+Sau khi ra trường, bạn có thể làm việc tại các công ty công nghệ, ngân hàng, công ty tài chính, thương mại điện tử, các doanh nghiệp sản xuất, và thậm chí cả các cơ quan nhà nước. Ngành có các chuyên ngành như: Khoa học Máy tính, Công nghệ dữ liệu và dữ liệu lớn, Công nghệ Phần mềm, An ninh hệ thống và mạng, Trí tuệ nhân tạo, Công nghệ Thông tin.</t>
   </si>
   <si>
     <t>Các môn cơ sở ngành bao gồm: Nhập môn điện toán, Cấu trúc rời rạc, Hệ thống số, Kỹ thuật lập trình, Cấu trúc dữ liệu và giải thuật, Kiến trúc máy tính, Mô hình hóa toán học, Hệ điều hành, Mạng máy tính, Công nghệ phần mềm, Lập trình nâng cao, Hệ cơ sở và dữ liệu, Nguyên lý ngôn ngữ lập trình. Sau tốt nghiệp, sinh viên có thể làm tại các công ty công nghệ, ngân hàng, công ty tài chính, thương mại điện tử, doanh nghiệp sản xuất và cơ quan nhà nước.</t>
   </si>
   <si>
+    <t>['Q: Ngành Khoa học máy tính sẽ học những môn gì chủ yếu\nA: Môn cơ sở ngành của ngành khoa học máy tính trường chúng tôi là: nhập môn điện toán, cấu trúc rời rạc, hệ thống số, kĩ thuật lập trình, cấu trúc dữ liệu và giải thuật, kiến trúc máy tính, mô hình hóa toán học, hệ điều hành, mạng máy tính, công nghệ phần mềm, lập trình nâng cao, hệ cơ sở và dữ liệu, nguyên lý ngôn ngữ lập trình. ', 'Q: Học ngành Khoa học máy tính ra có thể làm việc ở đâu\nA: Ngành khoa học máy tính của trường chúng tôi có các chuyên ngành như: Khoa học Máy tính, Công nghệ dữ liệu và dữ liệu lớn, Công nghệ Phần mềm, An ninh hệ thống và mạng, Trí tuệ nhân tạo,Công nghệ Thông tin. Các công ty công nghệ, ngân hàng, công ty tài chính, thương mại điện tử, các doanh nghiệp sản xuất, và thậm chí cả các cơ quan nhà nước đều có nhu cầu rất lớn về nhân lực khoa học máy tính.', 'Q: Sinh viên KHMT có được thực tập ở các công ty lớn không?\nA: Sinh viên ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM có nhiều cơ hội thực tập và làm việc tại các công ty lớn trong lĩnh vực công nghệ thông tin. Khoa Khoa học và Kỹ thuật Máy tính thường xuyên tổ chức các hoạt động hướng nghiệp và tạo điều kiện cho sinh viên tiếp cận với các doanh nghiệp, giúp họ tích lũy kinh nghiệm và kỹ năng thực tế.', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.', 'Q: Điểm chuẩn ngành Khoa học Máy tính các năm gần đây như thế nào?\nA: Điểm chuẩn ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM trong các năm gần đây có sự biến động. Cụ thể, điểm chuẩn của ngành này trong năm 2025 là 85.41 cho chương trình chính quy và 72.90 cho chương trình liên kết quốc tế với Úc, New Zealand, Mỹ.']</t>
+  </si>
+  <si>
     <t>0.8581808176935907</t>
   </si>
   <si>
-    <t>['Q: Xếp hạng của trường Đại học Bách khoa Thành phố Hồ Chí Minh là bao nhiêu\nA: Trường đạt các vị trí trong bảng xếp hạng Round University Ranking (RUR) năm 2024 như sau: 866 trong bảng xếp hạng “World University Rankings”, 432 trong bảng xếp hạng “RUR Reputation Rankings”, 776 trong bảng xếp hạng “RUR Academic Rankings”', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Số bài báo quốc tế của trường là bao nhiêu\nA: Trường chúng tôi có 1.190 bài báo quốc tế trong năm 2024', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.']</t>
-  </si>
-  <si>
-    <t>Trường đạt các vị trí trong bảng xếp hạng Round University Ranking (RUR) năm 2024 như sau: 866 trong bảng xếp hạng “World University Rankings”, 432 trong bảng xếp hạng “RUR Reputation Rankings”, 776 trong bảng xếp hạng “RUR Academic Rankings”.</t>
+    <t>Xếp hạng của Trường Đại học Bách khoa TP.HCM trong bảng xếp hạng RUR năm 2024 là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Trường đạt các vị trí trong bảng xếp hạng Round University Ranking (RUR) năm 2024 như sau: 866 trong bảng xếp hạng “World University Rankings”, 432 trong bảng xếp hạng “RUR Reputation Rankings”, 776 trong bảng xếp hạng “RUR Academic Rankings”.</t>
   </si>
   <si>
     <t>Trong bảng xếp hạng RUR năm 2024, trường đạt: hạng 866 (World University Rankings), hạng 432 (RUR Reputation Rankings), hạng 776 (RUR Academic Rankings).</t>
   </si>
   <si>
+    <t>['Q: Xếp hạng của trường Đại học Bách khoa Thành phố Hồ Chí Minh là bao nhiêu\nA: Trường đạt các vị trí trong bảng xếp hạng Round University Ranking (RUR) năm 2024 như sau: 866 trong bảng xếp hạng “World University Rankings”, 432 trong bảng xếp hạng “RUR Reputation Rankings”, 776 trong bảng xếp hạng “RUR Academic Rankings”', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu']</t>
+  </si>
+  <si>
     <t>0.7702125500723903</t>
   </si>
   <si>
-    <t>['Q: Trường có các chứng nhận kiểm định quốc tế về chương trình đào tạo không?\nA: Có. Trường chúng tôi có các kiểm định cấp chương trình đào tạo như ABET, FIBAA, IACEE', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Hãy kể tên các chương trình học bổng du học - chương trình trao đổi của trường \nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và trao đổi du học hấp dẫn cho sinh viên, bao gồm:Học bổng trao đổi và học bổng toàn phần Sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc),...Chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp, mang lại cơ hội học tập và trải nghiệm tại nước ngoài.Cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp,Chương trình Việt Pháp (PFIEV) cung cấp cơ hội học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp,Những chương trình này không chỉ hỗ trợ tài chính mà còn mở rộng cơ hội phát triển kỹ năng, kiến thức và kinh nghiệm quốc tế cho sinh viên.', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957']</t>
+    <t>Trường Bách khoa có những chứng nhận kiểm định quốc tế nào cho chương trình đào tạo?</t>
   </si>
   <si>
     <t>Có. Trường chúng tôi có các kiểm định cấp chương trình đào tạo như ABET, FIBAA, IACEE.</t>
@@ -389,28 +467,37 @@
     <t>Trường có các kiểm định cấp chương trình đào tạo quốc tế gồm: ABET, FIBAA và IACEE.</t>
   </si>
   <si>
+    <t>['Q: Trường có các chứng nhận kiểm định quốc tế về chương trình đào tạo không?\nA: Có. Trường chúng tôi có các kiểm định cấp chương trình đào tạo như ABET, FIBAA, IACEE', 'Q: Trường mình có các ngành đào tạo nào\nA: Trường Đại học Bách khoa - ĐHQG-HCM hiện có nhiều chương trình đào tạo đa dạng, bao gồm các chương trình tiêu chuẩn, chương trình dạy và học bằng tiếng Anh, chương trình chuyển tiếp quốc tế, chương trình liên kết quốc tế, và chương trình định hướng Nhật Bản.Một số ngành đào tạo chính của trường bao gồm:Khoa học Máy tính,Kỹ thuật Máy tính,Kỹ thuật Điện - Điện tử,Kỹ thuật Cơ khí,Kỹ thuật Cơ Điện tử,Kỹ thuật Hóa học,Công nghệ Sinh học,Công nghệ Thực phẩm,Quản lý Dự án Xây dựng và Kỹ thuật Xây dựng,Kiến trúc,Kỹ thuật Dầu khí,Quản lý Công nghiệp,Tài nguyên và Môi trường,Logistics và Hệ thống Công nghiệp,Kỹ thuật Vật liệu,Vật lý Kỹ thuật,Cơ Kỹ thuật,Khoa học Dữ liệu,Kỹ thuật Ô tô,Kỹ thuật Hàng không.', 'Q: Thông tin chi tiết về học phí và học bổng của trường là gì?\nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình đào tạo với mức học phí khác nhau. Dưới đây là một số thông tin về học phí và học bổng:Học phí cho các chương trình đào tạo:- Chương trình CQ (Tiêu chuẩn), PFIEV (Kỹ sư Chất lượng cao tại Việt-Pháp): khoảng 15 triệu đồng/học kỳ.- Chương trình CTTT (Tiên tiến), CTTA (Dạy và học bằng tiếng Anh), CTQT (Chuyển tiếp Quốc tế Úc, Mỹ, New Zealand): khoảng 40 triệu đồng/học kỳ (trừ các ngành mới năm 2025 có mức ưu đãi).- Chương trình CTNB (Chuyển tiếp Quốc tế Nhật Bản) / CTHNB (Định hướng Nhật Bản): khoảng 30 triệu đồng/học kỳ.- Chương trình TNE (Liên kết Cử nhân Kỹ thuật Quốc tế): khoảng 128 triệu đồng/học kỳ.Về học bổng, Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều loại học bổng khác nhau, bao gồm:Học bổng khuyến khích học tập: trị giá lên tới 120% giá trị học phí/học kỳ/suất.Quỹ học bổng và Hỗ trợ phát triển Bách khoa: 40 tỷ đồng.Học bổng tài trợ từ các đối tác nước ngoài, tổ chức, doanh nghiệp: hơn 16 tỷ đồng.Học bổng dành cho sinh viên chương trình đào tạo quốc tế.Chương trình vay ưu đãi với lãi suất 0% để học tập của ĐHQG-HCM.Chương trình Bảo lãnh vay và hỗ trợ lãi suất của Ban Đại diện Cộng đồng Cựu sinh viên Phú Thọ - Bách khoa.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Hãy kể tên các chương trình học bổng du học - chương trình trao đổi của trường \nA: Trường Đại học Bách khoa - ĐHQG-HCM cung cấp nhiều chương trình học bổng và trao đổi du học hấp dẫn cho sinh viên, bao gồm:Học bổng trao đổi và học bổng toàn phần Sau đại học tại các trường đại học đối tác quốc tế như University of Technology, Sydney (Úc), Nanyang University of Technology (Singapore), University of Newcastle (Úc), Pukyong National University (Hàn Quốc),...Chương trình trao đổi sinh viên với các trường đại học đối tác tại Pháp, mang lại cơ hội học tập và trải nghiệm tại nước ngoài.Cơ hội nhận học bổng vùng, học bổng EIFFEL, học bổng ERASMUS cho sinh viên tham gia chương trình trao đổi hoặc thực tập tại Pháp,Chương trình Việt Pháp (PFIEV) cung cấp cơ hội học 2 năm tại Pháp hoặc thực tập tốt nghiệp 6 tháng tại Pháp,Những chương trình này không chỉ hỗ trợ tài chính mà còn mở rộng cơ hội phát triển kỹ năng, kiến thức và kinh nghiệm quốc tế cho sinh viên.']</t>
+  </si>
+  <si>
     <t>0.765753086238637</t>
   </si>
   <si>
-    <t>['Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Trường mình tên đầy đủ là gì ạ\nA: Tên đầy đủ của trường chúng tôi là Trường Đại học Bách khoa Thành phố Hồ Chí Minh', 'Q: Tầm nhìn của trường hiện tại là gì?\nA: Được công nhận toàn cầu là Trường Đại học hàng đầu trong khu vực về giảng dạy, học tập, nghiên cứu và khởi nghiệp – đổi mới sáng tạo.', 'Q: Khẩu hiệu của trường là gì?\nA: Khẩu hiệu của trường là Khai phóng, Tiên phong, Sáng tạo']</t>
-  </si>
-  <si>
-    <t>Khẩu hiệu của trường là Khai phóng, Tiên phong, Sáng tạo. Tầm nhìn của trường là Được công nhận toàn cầu là Trường Đại học hàng đầu trong khu vực về giảng dạy, học tập, nghiên cứu và khởi nghiệp – đổi mới sáng tạo.</t>
+    <t>Khẩu hiệu và tầm nhìn của Trường Đại học Bách khoa TP.HCM là gì?</t>
+  </si>
+  <si>
+    <t>Trường Đại học Bách khoa TP.HCM (HCMUT) có khẩu hiệu là "Khai phóng, Tiên phong, Sáng tạo" và tầm nhìn là "Được công nhận toàn cầu là Trường Đại học hàng đầu trong khu vực về giảng dạy, học tập, nghiên cứu và khởi nghiệp – đổi mới sáng tạo".</t>
   </si>
   <si>
     <t>Khẩu hiệu của trường là "Khai phóng - Tiên phong - Sáng tạo". Tầm nhìn là được công nhận toàn cầu là trường đại học hàng đầu trong khu vực về giảng dạy, học tập, nghiên cứu và khởi nghiệp – đổi mới sáng tạo.</t>
   </si>
   <si>
+    <t>['Q: Tầm nhìn của trường hiện tại là gì?\nA: Được công nhận toàn cầu là Trường Đại học hàng đầu trong khu vực về giảng dạy, học tập, nghiên cứu và khởi nghiệp – đổi mới sáng tạo.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.', 'Q: Khẩu hiệu của trường là gì?\nA: Khẩu hiệu của trường là Khai phóng, Tiên phong, Sáng tạo', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957']</t>
+  </si>
+  <si>
     <t>0.7835184026461289</t>
   </si>
   <si>
-    <t>['Q: Làm sao để liên hệ trực tiếp với khoa Khoa học Máy tính?\nA: Để liên hệ trực tiếp với Khoa Khoa học và Kỹ thuật Máy tính (CSE) tại Trường Đại học Bách khoa - ĐHQG-HCM, bạn có thể tìm thông tin liên lạc từ Trưởng khoa hoặc các Phó Trưởng khoa. Trưởng khoa hiện tại là PGS. TS. Quản Thành Thơ với email qttho@hcmut.edu.vn.', 'Q: Địa chỉ email của trường là gì?\nA: Địa chỉ email của Trường Đại học Bách khoa - ĐHQG-HCM là info@hcmut.edu.vn.', 'Q: Chỉ tiêu tuyển sinh ngành Khoa học máy tính năm 2025 là bao nhiêu\nA: Năm 2025, chỉ tiêu tuyển sinh ngành Khoa học Máy tính của Trường Đại học Bách khoa - Đại học Quốc gia TP.HCM là 150 chỉ tiêu', 'Q: Điểm chuẩn ngành Khoa học Máy tính các năm gần đây như thế nào?\nA: Điểm chuẩn ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM trong các năm gần đây có sự biến động. Cụ thể, điểm chuẩn của ngành này trong năm 2025 là 85.41 cho chương trình chính quy và 72.90 cho chương trình liên kết quốc tế với Úc, New Zealand, Mỹ.', 'Q: Hiệu trưởng hiện tại của trường là ai\nA: Hiệu trưởng Trường Đại học Bách khoa (HCMUT) hiện tại là PGS. TS. Mai Thanh Phong. Ông được bổ nhiệm vào chức vụ này vào tháng 5 năm 2018.']</t>
-  </si>
-  <si>
-    <t>Để liên hệ trực tiếp với Khoa Khoa học và Kỹ thuật Máy tính (CSE) tại Trường Đại học Bách khoa TP.HCM, bạn có thể gửi email cho PGS. TS. Quản Thành Thơ với địa chỉ email qttho@hcmut.edu.vn.</t>
+    <t>Em muốn liên hệ với Khoa Khoa học và Kỹ thuật Máy tính thì gửi email cho ai và địa chỉ email là gì?</t>
+  </si>
+  <si>
+    <t>Để liên hệ với Khoa Khoa học và Kỹ thuật Máy tính, bạn có thể gửi email cho PGS. TS. Quản Thành Thơ, Trưởng khoa, với địa chỉ email qttho@hcmut.edu.vn.</t>
   </si>
   <si>
     <t>Bạn có thể liên hệ với Trưởng khoa CSE là PGS. TS. Quản Thành Thơ qua email: qttho@hcmut.edu.vn.</t>
+  </si>
+  <si>
+    <t>['Q: Làm sao để liên hệ trực tiếp với khoa Khoa học Máy tính?\nA: Để liên hệ trực tiếp với Khoa Khoa học và Kỹ thuật Máy tính (CSE) tại Trường Đại học Bách khoa - ĐHQG-HCM, bạn có thể tìm thông tin liên lạc từ Trưởng khoa hoặc các Phó Trưởng khoa. Trưởng khoa hiện tại là PGS. TS. Quản Thành Thơ với email qttho@hcmut.edu.vn.', 'Q: Địa chỉ email của trường là gì?\nA: Địa chỉ email của Trường Đại học Bách khoa - ĐHQG-HCM là info@hcmut.edu.vn.', 'Q: Trường mình có tên viết tắt là gì ?\nA: Trường mình có tên viết tắt là HCMUT ', 'Q: Trường thành lập từ năm nào vậy\nA: Trường chúng tôi được thành lập từ năm 1957', 'Q: Sinh viên KHMT có được thực tập ở các công ty lớn không?\nA: Sinh viên ngành Khoa học Máy tính tại Trường Đại học Bách khoa - ĐHQG-HCM có nhiều cơ hội thực tập và làm việc tại các công ty lớn trong lĩnh vực công nghệ thông tin. Khoa Khoa học và Kỹ thuật Máy tính thường xuyên tổ chức các hoạt động hướng nghiệp và tạo điều kiện cho sinh viên tiếp cận với các doanh nghiệp, giúp họ tích lũy kinh nghiệm và kỹ năng thực tế.']</t>
   </si>
   <si>
     <t>0.8247141498889331</t>
@@ -426,7 +513,14 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -899,133 +993,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1033,9 +1127,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -1575,52 +1667,56 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
+    <col min="1" max="1" width="128.222222222222" customWidth="1"/>
     <col min="2" max="4" width="255.777777777778" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="20.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="E2">
         <v>0.583</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1630,23 +1726,23 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1656,23 +1752,23 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1682,23 +1778,23 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="E5">
         <v>0.9999999999</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1708,23 +1804,23 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="E6">
         <v>0.9999999999</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1734,23 +1830,23 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="E7">
         <v>0.9999999999</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1760,23 +1856,23 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
+      <c r="A8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E8">
         <v>0.9999999999</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1786,23 +1882,23 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
+      <c r="A9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="E9">
         <v>0.9999999999</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1812,23 +1908,23 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
+      <c r="A10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="E10">
         <v>0.9999999999</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1838,23 +1934,23 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
+      <c r="A11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="E11">
         <v>0.99999999995</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1864,23 +1960,23 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" t="s">
-        <v>49</v>
+      <c r="A12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="E12">
         <v>0.9999999999</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1890,23 +1986,23 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
+      <c r="A13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="E13">
         <v>0.9999999999</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1915,24 +2011,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="43.2" spans="1:8">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>55</v>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
+        <v>69</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="E14">
         <v>0.9999999999</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1942,23 +2038,23 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" t="s">
-        <v>61</v>
+      <c r="A15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="E15">
         <v>0.99999999995</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1968,23 +2064,23 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" t="s">
-        <v>65</v>
+      <c r="A16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="E16">
         <v>0.9999999999</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1994,46 +2090,49 @@
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" t="s">
-        <v>69</v>
+      <c r="A17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
+      <c r="A18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="E18">
         <v>0.9999999999</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -2043,46 +2142,49 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" t="s">
-        <v>77</v>
+      <c r="A19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="E19">
         <v>0.9999999999</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>79</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>81</v>
+      <c r="A20" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -2092,23 +2194,23 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>85</v>
+      <c r="A21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="E21">
         <v>0.9999999999</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -2118,23 +2220,23 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D22" t="s">
-        <v>89</v>
+      <c r="A22" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -2144,23 +2246,23 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>93</v>
+      <c r="A23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2169,24 +2271,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="86.4" spans="1:8">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>95</v>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>97</v>
+        <v>119</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="E24">
         <v>0.9999999999</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -2196,23 +2298,23 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" t="s">
-        <v>101</v>
+      <c r="A25" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="E25">
         <v>0.9999999999</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -2222,23 +2324,23 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" t="s">
-        <v>105</v>
+      <c r="A26" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="E26">
         <v>0.9999999999</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>106</v>
+        <v>131</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2247,24 +2349,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="57.6" spans="1:8">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27" t="s">
-        <v>107</v>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>109</v>
+        <v>134</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2274,23 +2376,23 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" t="s">
-        <v>113</v>
+      <c r="A28" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="E28">
         <v>0.9999999999</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2300,23 +2402,23 @@
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" t="s">
-        <v>117</v>
+      <c r="A29" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>145</v>
       </c>
       <c r="E29">
         <v>0.9999999999</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2326,23 +2428,23 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" t="s">
-        <v>121</v>
+      <c r="A30" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2352,23 +2454,23 @@
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C31" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" t="s">
-        <v>125</v>
+      <c r="A31" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="E31">
         <v>0.9999999999</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="G31">
         <v>1</v>
